--- a/salidas/empresas/MCK.xlsx
+++ b/salidas/empresas/MCK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>45.41143417358398</v>
+        <v>45.41146087646484</v>
       </c>
       <c r="C2" t="n">
         <v>53</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>46.43163299560547</v>
+        <v>46.43162155151367</v>
       </c>
       <c r="C3" t="n">
         <v>54.13000106811523</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>44.71607971191406</v>
+        <v>44.716064453125</v>
       </c>
       <c r="C4" t="n">
         <v>52.13000106811523</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>41.67953491210938</v>
+        <v>41.67954254150391</v>
       </c>
       <c r="C5" t="n">
         <v>48.59000015258789</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.46010971069336</v>
+        <v>42.4600944519043</v>
       </c>
       <c r="C6" t="n">
         <v>49.5</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>40.60649490356445</v>
+        <v>40.60650634765625</v>
       </c>
       <c r="C7" t="n">
         <v>47.27999877929688</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>43.27752304077148</v>
+        <v>43.27751159667969</v>
       </c>
       <c r="C8" t="n">
         <v>50.38999938964844</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>43.68072128295898</v>
+        <v>43.68072509765625</v>
       </c>
       <c r="C9" t="n">
         <v>50.79999923706055</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>45.33167266845703</v>
+        <v>45.33164978027344</v>
       </c>
       <c r="C10" t="n">
         <v>52.72000122070312</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>43.07022476196289</v>
+        <v>43.07024002075195</v>
       </c>
       <c r="C11" t="n">
         <v>50.09000015258789</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>43.64874649047852</v>
+        <v>43.64873886108398</v>
       </c>
       <c r="C13" t="n">
         <v>50.70000076293945</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>47.99639892578125</v>
+        <v>47.99639511108398</v>
       </c>
       <c r="C14" t="n">
         <v>55.75</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>48.02101135253906</v>
+        <v>48.02099609375</v>
       </c>
       <c r="C15" t="n">
         <v>55.72000122070312</v>
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>50.70129013061523</v>
+        <v>50.70128631591797</v>
       </c>
       <c r="C17" t="n">
         <v>58.83000183105469</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>54.40715026855469</v>
+        <v>54.40715789794922</v>
       </c>
       <c r="C18" t="n">
         <v>63.13000106811523</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>51.44898986816406</v>
+        <v>51.44898223876953</v>
       </c>
       <c r="C19" t="n">
         <v>59.63999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.82717895507812</v>
+        <v>49.82718276977539</v>
       </c>
       <c r="C20" t="n">
         <v>57.7599983215332</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>49.40350723266602</v>
+        <v>49.40353012084961</v>
       </c>
       <c r="C21" t="n">
         <v>57.20999908447266</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>57.0804328918457</v>
+        <v>57.08042526245117</v>
       </c>
       <c r="C23" t="n">
         <v>66.09999847412109</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.67609786987305</v>
+        <v>57.67607498168945</v>
       </c>
       <c r="C24" t="n">
         <v>66.73000335693359</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>56.62159729003906</v>
+        <v>56.62164306640625</v>
       </c>
       <c r="C25" t="n">
         <v>65.51000213623047</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>45.3092041015625</v>
+        <v>45.30920028686523</v>
       </c>
       <c r="C28" t="n">
         <v>52.36999893188477</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>45.09292602539062</v>
+        <v>45.09291839599609</v>
       </c>
       <c r="C29" t="n">
         <v>52.11999893188477</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>49.8773307800293</v>
+        <v>49.87733840942383</v>
       </c>
       <c r="C30" t="n">
         <v>57.65000152587891</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.47301864624023</v>
+        <v>48.4730339050293</v>
       </c>
       <c r="C31" t="n">
         <v>55.90999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>48.54238510131836</v>
+        <v>48.54239273071289</v>
       </c>
       <c r="C32" t="n">
         <v>55.9900016784668</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>50.1981201171875</v>
+        <v>50.19811630249023</v>
       </c>
       <c r="C33" t="n">
         <v>57.77999877929688</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>46.74907302856445</v>
+        <v>46.74905776977539</v>
       </c>
       <c r="C34" t="n">
         <v>53.81000137329102</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>30.46602058410645</v>
+        <v>30.46602821350098</v>
       </c>
       <c r="C36" t="n">
         <v>34.93999862670898</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>33.77073669433594</v>
+        <v>33.7707405090332</v>
       </c>
       <c r="C37" t="n">
         <v>38.72999954223633</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>38.54031372070312</v>
+        <v>38.54032135009766</v>
       </c>
       <c r="C38" t="n">
         <v>44.20000076293945</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>35.86599731445312</v>
+        <v>35.86600875854492</v>
       </c>
       <c r="C39" t="n">
         <v>41.02000045776367</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>30.63735198974609</v>
+        <v>30.63735580444336</v>
       </c>
       <c r="C40" t="n">
         <v>35.04000091552734</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>35.97966766357422</v>
+        <v>35.97964477539062</v>
       </c>
       <c r="C42" t="n">
         <v>41.15000152587891</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>38.58282089233398</v>
+        <v>38.58280944824219</v>
       </c>
       <c r="C43" t="n">
         <v>44</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>49.96472930908203</v>
+        <v>49.9647216796875</v>
       </c>
       <c r="C45" t="n">
         <v>56.86000061035156</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>52.3285026550293</v>
+        <v>52.32852554321289</v>
       </c>
       <c r="C46" t="n">
         <v>59.54999923706055</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>51.60794448852539</v>
+        <v>51.60794067382812</v>
       </c>
       <c r="C47" t="n">
         <v>58.72999954223633</v>
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>55.02463912963867</v>
+        <v>55.02463531494141</v>
       </c>
       <c r="C49" t="n">
         <v>62.5</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>51.7848014831543</v>
+        <v>51.78478622436523</v>
       </c>
       <c r="C50" t="n">
         <v>58.81999969482422</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>52.18097686767578</v>
+        <v>52.18096923828125</v>
       </c>
       <c r="C51" t="n">
         <v>59.15000152587891</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>57.97690582275391</v>
+        <v>57.97689056396484</v>
       </c>
       <c r="C52" t="n">
         <v>65.72000122070312</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>57.17411422729492</v>
+        <v>57.17411804199219</v>
       </c>
       <c r="C53" t="n">
         <v>64.80999755859375</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>61.75262832641602</v>
+        <v>61.75263214111328</v>
       </c>
       <c r="C54" t="n">
         <v>70</v>
@@ -1559,11 +1571,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>59.40231704711914</v>
+        <v>59.40231323242188</v>
       </c>
       <c r="C55" t="n">
         <v>67.16000366210938</v>
@@ -1588,11 +1600,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>55.56362533569336</v>
+        <v>55.56362915039062</v>
       </c>
       <c r="C56" t="n">
         <v>62.81999969482422</v>
@@ -1617,11 +1629,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>51.4981689453125</v>
+        <v>51.49818420410156</v>
       </c>
       <c r="C57" t="n">
         <v>58.04999923706055</v>
@@ -1646,11 +1658,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>54.80718994140625</v>
+        <v>54.80719375610352</v>
       </c>
       <c r="C58" t="n">
         <v>61.77999877929688</v>
@@ -1675,11 +1687,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.53316116333008</v>
+        <v>58.53316879272461</v>
       </c>
       <c r="C59" t="n">
         <v>65.98000335693359</v>
@@ -1704,11 +1716,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>56.84653854370117</v>
+        <v>56.84653091430664</v>
       </c>
       <c r="C60" t="n">
         <v>63.90000152587891</v>
@@ -1733,11 +1745,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>62.61124801635742</v>
+        <v>62.61124420166016</v>
       </c>
       <c r="C61" t="n">
         <v>70.37999725341797</v>
@@ -1762,11 +1774,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>66.87252044677734</v>
+        <v>66.87253570556641</v>
       </c>
       <c r="C62" t="n">
         <v>75.16999816894531</v>
@@ -1791,11 +1803,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>70.69151306152344</v>
+        <v>70.69154357910156</v>
       </c>
       <c r="C63" t="n">
         <v>79.27999877929688</v>
@@ -1820,11 +1832,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>70.48647308349609</v>
+        <v>70.48646545410156</v>
       </c>
       <c r="C64" t="n">
         <v>79.05000305175781</v>
@@ -1849,7 +1861,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1878,11 +1890,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>76.33580780029297</v>
+        <v>76.33580017089844</v>
       </c>
       <c r="C66" t="n">
         <v>85.61000061035156</v>
@@ -1907,11 +1919,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>74.76538848876953</v>
+        <v>74.76541900634766</v>
       </c>
       <c r="C67" t="n">
         <v>83.65000152587891</v>
@@ -1936,11 +1948,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>72.50411987304688</v>
+        <v>72.50414276123047</v>
       </c>
       <c r="C68" t="n">
         <v>81.12000274658203</v>
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1994,11 +2006,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>65.14517974853516</v>
+        <v>65.14521026611328</v>
       </c>
       <c r="C70" t="n">
         <v>72.69999694824219</v>
@@ -2023,11 +2035,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>73.07551574707031</v>
+        <v>73.07554626464844</v>
       </c>
       <c r="C71" t="n">
         <v>81.55000305175781</v>
@@ -2052,11 +2064,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>73.04718780517578</v>
+        <v>73.04716491699219</v>
       </c>
       <c r="C72" t="n">
         <v>81.30999755859375</v>
@@ -2081,11 +2093,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>69.99271392822266</v>
+        <v>69.99267578125</v>
       </c>
       <c r="C73" t="n">
         <v>77.91000366210938</v>
@@ -2110,11 +2122,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>73.41554260253906</v>
+        <v>73.41551971435547</v>
       </c>
       <c r="C74" t="n">
         <v>81.72000122070312</v>
@@ -2139,11 +2151,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>75.20680236816406</v>
+        <v>75.20679473876953</v>
       </c>
       <c r="C75" t="n">
         <v>83.51000213623047</v>
@@ -2168,11 +2180,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>79.04325103759766</v>
+        <v>79.04324340820312</v>
       </c>
       <c r="C76" t="n">
         <v>87.76999664306641</v>
@@ -2197,7 +2209,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2226,11 +2238,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>78.60195922851562</v>
+        <v>78.60196685791016</v>
       </c>
       <c r="C78" t="n">
         <v>87.27999877929688</v>
@@ -2255,11 +2267,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>84.62190246582031</v>
+        <v>84.62193298339844</v>
       </c>
       <c r="C79" t="n">
         <v>93.75</v>
@@ -2284,7 +2296,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2313,7 +2325,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2342,11 +2354,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>77.83065795898438</v>
+        <v>77.83067321777344</v>
       </c>
       <c r="C82" t="n">
         <v>86.02999877929688</v>
@@ -2371,11 +2383,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>84.41681671142578</v>
+        <v>84.41683197021484</v>
       </c>
       <c r="C83" t="n">
         <v>93.30999755859375</v>
@@ -2400,7 +2412,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2429,11 +2441,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>87.90808868408203</v>
+        <v>87.90805053710938</v>
       </c>
       <c r="C85" t="n">
         <v>96.95999908447266</v>
@@ -2458,11 +2470,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>95.40597534179688</v>
+        <v>95.406005859375</v>
       </c>
       <c r="C86" t="n">
         <v>105.2300033569336</v>
@@ -2487,11 +2499,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>96.40724182128906</v>
+        <v>96.40723419189453</v>
       </c>
       <c r="C87" t="n">
         <v>106.129997253418</v>
@@ -2516,11 +2528,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>98.06959533691406</v>
+        <v>98.06957244873047</v>
       </c>
       <c r="C88" t="n">
         <v>107.9599990844727</v>
@@ -2545,11 +2557,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>96.12564086914062</v>
+        <v>96.1256103515625</v>
       </c>
       <c r="C89" t="n">
         <v>105.8199996948242</v>
@@ -2574,11 +2586,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>103.4290771484375</v>
+        <v>103.429069519043</v>
       </c>
       <c r="C90" t="n">
         <v>113.8600006103516</v>
@@ -2603,7 +2615,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2632,11 +2644,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>111.6216430664062</v>
+        <v>111.6216659545898</v>
       </c>
       <c r="C92" t="n">
         <v>122.6600036621094</v>
@@ -2661,11 +2673,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>110.703369140625</v>
+        <v>110.7033920288086</v>
       </c>
       <c r="C93" t="n">
         <v>121.4100036621094</v>
@@ -2690,11 +2702,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>116.9857864379883</v>
+        <v>116.9857940673828</v>
       </c>
       <c r="C94" t="n">
         <v>128.3000030517578</v>
@@ -2719,11 +2731,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>142.5531005859375</v>
+        <v>142.5530242919922</v>
       </c>
       <c r="C95" t="n">
         <v>156.3399963378906</v>
@@ -2748,11 +2760,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>151.4821166992188</v>
+        <v>151.4820709228516</v>
       </c>
       <c r="C96" t="n">
         <v>165.8899993896484</v>
@@ -2777,11 +2789,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>147.3820495605469</v>
+        <v>147.3820190429688</v>
       </c>
       <c r="C97" t="n">
         <v>161.3999938964844</v>
@@ -2806,11 +2818,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>159.2621307373047</v>
+        <v>159.2620544433594</v>
       </c>
       <c r="C98" t="n">
         <v>174.4100036621094</v>
@@ -2835,11 +2847,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>161.8951110839844</v>
+        <v>161.8950805664062</v>
       </c>
       <c r="C99" t="n">
         <v>177.0500030517578</v>
@@ -2864,7 +2876,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2893,7 +2905,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2922,11 +2934,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>173.4074096679688</v>
+        <v>173.407470703125</v>
       </c>
       <c r="C102" t="n">
         <v>189.6399993896484</v>
@@ -2951,11 +2963,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>170.4866943359375</v>
+        <v>170.4866790771484</v>
       </c>
       <c r="C103" t="n">
         <v>186.2100067138672</v>
@@ -2980,11 +2992,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>175.6596069335938</v>
+        <v>175.6595611572266</v>
       </c>
       <c r="C104" t="n">
         <v>191.8600006103516</v>
@@ -3009,11 +3021,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>178.7853393554688</v>
+        <v>178.7854309082031</v>
       </c>
       <c r="C105" t="n">
         <v>195.0299987792969</v>
@@ -3038,11 +3050,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>178.4553833007812</v>
+        <v>178.4553375244141</v>
       </c>
       <c r="C106" t="n">
         <v>194.6699981689453</v>
@@ -3067,11 +3079,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>186.4673767089844</v>
+        <v>186.4673156738281</v>
       </c>
       <c r="C107" t="n">
         <v>203.4100036621094</v>
@@ -3096,7 +3108,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3125,11 +3137,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>190.5088500976562</v>
+        <v>190.5089111328125</v>
       </c>
       <c r="C109" t="n">
         <v>207.5800018310547</v>
@@ -3154,11 +3166,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>195.1619415283203</v>
+        <v>195.1619262695312</v>
       </c>
       <c r="C110" t="n">
         <v>212.6499938964844</v>
@@ -3183,11 +3195,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>210.1116180419922</v>
+        <v>210.1116485595703</v>
       </c>
       <c r="C111" t="n">
         <v>228.6999969482422</v>
@@ -3212,7 +3224,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3241,11 +3253,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>205.2424011230469</v>
+        <v>205.2424163818359</v>
       </c>
       <c r="C113" t="n">
         <v>223.3999938964844</v>
@@ -3270,11 +3282,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>217.9482879638672</v>
+        <v>217.9483337402344</v>
       </c>
       <c r="C114" t="n">
         <v>237.2299957275391</v>
@@ -3299,7 +3311,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3328,11 +3340,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>202.8477783203125</v>
+        <v>202.8478546142578</v>
       </c>
       <c r="C116" t="n">
         <v>220.5700073242188</v>
@@ -3357,11 +3369,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>181.961181640625</v>
+        <v>181.9612426757812</v>
       </c>
       <c r="C117" t="n">
         <v>197.5800018310547</v>
@@ -3386,11 +3398,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>170.4032287597656</v>
+        <v>170.4032897949219</v>
       </c>
       <c r="C118" t="n">
         <v>185.0299987792969</v>
@@ -3415,11 +3427,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>164.6657409667969</v>
+        <v>164.6658020019531</v>
       </c>
       <c r="C119" t="n">
         <v>178.8000030517578</v>
@@ -3444,11 +3456,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>174.6396942138672</v>
+        <v>174.6397399902344</v>
       </c>
       <c r="C120" t="n">
         <v>189.3500061035156</v>
@@ -3473,11 +3485,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>181.9074554443359</v>
+        <v>181.9075164794922</v>
       </c>
       <c r="C121" t="n">
         <v>197.2299957275391</v>
@@ -3502,11 +3514,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>148.4737548828125</v>
+        <v>148.4737091064453</v>
       </c>
       <c r="C122" t="n">
         <v>160.9799957275391</v>
@@ -3531,11 +3543,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>143.7892761230469</v>
+        <v>143.7892456054688</v>
       </c>
       <c r="C123" t="n">
         <v>155.6199951171875</v>
@@ -3560,11 +3572,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>145.2953186035156</v>
+        <v>145.2953643798828</v>
       </c>
       <c r="C124" t="n">
         <v>157.25</v>
@@ -3589,11 +3601,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>155.0618133544922</v>
+        <v>155.0617980957031</v>
       </c>
       <c r="C125" t="n">
         <v>167.8200073242188</v>
@@ -3618,7 +3630,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3647,11 +3659,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>172.7219543457031</v>
+        <v>172.7219390869141</v>
       </c>
       <c r="C127" t="n">
         <v>186.6499938964844</v>
@@ -3676,11 +3688,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>180.0417175292969</v>
+        <v>180.0417327880859</v>
       </c>
       <c r="C128" t="n">
         <v>194.5599975585938</v>
@@ -3705,11 +3717,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>171.1039428710938</v>
+        <v>171.1039276123047</v>
       </c>
       <c r="C129" t="n">
         <v>184.6199951171875</v>
@@ -3734,11 +3746,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>154.542236328125</v>
+        <v>154.5421905517578</v>
       </c>
       <c r="C130" t="n">
         <v>166.75</v>
@@ -3763,11 +3775,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>117.8598709106445</v>
+        <v>117.8598785400391</v>
       </c>
       <c r="C131" t="n">
         <v>127.1699981689453</v>
@@ -3792,7 +3804,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3821,7 +3833,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3850,11 +3862,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>129.2156372070312</v>
+        <v>129.2156219482422</v>
       </c>
       <c r="C134" t="n">
         <v>139.1499938964844</v>
@@ -3879,11 +3891,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>139.6710052490234</v>
+        <v>139.6710357666016</v>
       </c>
       <c r="C135" t="n">
         <v>150.1300048828125</v>
@@ -3908,11 +3920,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>137.9312896728516</v>
+        <v>137.9312133789062</v>
       </c>
       <c r="C136" t="n">
         <v>148.2599945068359</v>
@@ -3937,11 +3949,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>128.6558685302734</v>
+        <v>128.6558380126953</v>
       </c>
       <c r="C137" t="n">
         <v>138.2899932861328</v>
@@ -3966,11 +3978,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>151.7280883789062</v>
+        <v>151.7281188964844</v>
       </c>
       <c r="C138" t="n">
         <v>163.0899963378906</v>
@@ -3995,11 +4007,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>153.3403778076172</v>
+        <v>153.3403015136719</v>
       </c>
       <c r="C139" t="n">
         <v>164.5399932861328</v>
@@ -4024,11 +4036,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>150.8521423339844</v>
+        <v>150.8520812988281</v>
       </c>
       <c r="C140" t="n">
         <v>161.8699951171875</v>
@@ -4053,11 +4065,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>139.4691619873047</v>
+        <v>139.4691009521484</v>
       </c>
       <c r="C141" t="n">
         <v>149.3099975585938</v>
@@ -4082,11 +4094,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>143.4857482910156</v>
+        <v>143.4856872558594</v>
       </c>
       <c r="C142" t="n">
         <v>153.6100006103516</v>
@@ -4111,7 +4123,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4140,11 +4152,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>138.320068359375</v>
+        <v>138.3200988769531</v>
       </c>
       <c r="C144" t="n">
         <v>147.7400054931641</v>
@@ -4169,11 +4181,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>146.0066375732422</v>
+        <v>146.0066986083984</v>
       </c>
       <c r="C145" t="n">
         <v>155.9499969482422</v>
@@ -4198,11 +4210,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>158.1122131347656</v>
+        <v>158.1122283935547</v>
       </c>
       <c r="C146" t="n">
         <v>168.8800048828125</v>
@@ -4227,11 +4239,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>140.02490234375</v>
+        <v>140.0248565673828</v>
       </c>
       <c r="C147" t="n">
         <v>149.2299957275391</v>
@@ -4256,11 +4268,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>132.1805725097656</v>
+        <v>132.1806030273438</v>
       </c>
       <c r="C148" t="n">
         <v>140.8699951171875</v>
@@ -4285,11 +4297,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>146.5743865966797</v>
+        <v>146.5743713378906</v>
       </c>
       <c r="C149" t="n">
         <v>156.2100067138672</v>
@@ -4314,11 +4326,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>133.4988861083984</v>
+        <v>133.4988403320312</v>
       </c>
       <c r="C150" t="n">
         <v>141.9400024414062</v>
@@ -4343,11 +4355,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>125.4667053222656</v>
+        <v>125.4667205810547</v>
       </c>
       <c r="C151" t="n">
         <v>133.3999938964844</v>
@@ -4372,11 +4384,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>118.1305847167969</v>
+        <v>118.1305923461914</v>
       </c>
       <c r="C152" t="n">
         <v>125.5999984741211</v>
@@ -4399,11 +4411,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>121.4576721191406</v>
+        <v>121.4576568603516</v>
       </c>
       <c r="C153" t="n">
         <v>128.75</v>
@@ -4426,11 +4438,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>125.1367874145508</v>
+        <v>125.1367721557617</v>
       </c>
       <c r="C154" t="n">
         <v>132.6499938964844</v>
@@ -4453,11 +4465,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>117.6936874389648</v>
+        <v>117.6936798095703</v>
       </c>
       <c r="C155" t="n">
         <v>124.7600021362305</v>
@@ -4482,11 +4494,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>117.8101501464844</v>
+        <v>117.8101654052734</v>
       </c>
       <c r="C156" t="n">
         <v>124.5</v>
@@ -4511,11 +4523,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>104.5340423583984</v>
+        <v>104.5340347290039</v>
       </c>
       <c r="C157" t="n">
         <v>110.4700012207031</v>
@@ -4540,11 +4552,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>121.3586349487305</v>
+        <v>121.3586502075195</v>
       </c>
       <c r="C158" t="n">
         <v>128.25</v>
@@ -4567,11 +4579,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>120.6966323852539</v>
+        <v>120.6966247558594</v>
       </c>
       <c r="C159" t="n">
         <v>127.1600036621094</v>
@@ -4594,11 +4606,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>111.1100082397461</v>
+        <v>111.1100158691406</v>
       </c>
       <c r="C160" t="n">
         <v>117.0599975585938</v>
@@ -4621,11 +4633,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>113.1886978149414</v>
+        <v>113.1886749267578</v>
       </c>
       <c r="C161" t="n">
         <v>119.25</v>
@@ -4648,11 +4660,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>116.2980346679688</v>
+        <v>116.2980270385742</v>
       </c>
       <c r="C162" t="n">
         <v>122.1399993896484</v>
@@ -4677,11 +4689,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>127.9620819091797</v>
+        <v>127.9621353149414</v>
       </c>
       <c r="C163" t="n">
         <v>134.3899993896484</v>
@@ -4706,7 +4718,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4735,11 +4747,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>132.0489654541016</v>
+        <v>132.0489349365234</v>
       </c>
       <c r="C165" t="n">
         <v>138.2700042724609</v>
@@ -4764,11 +4776,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>130.5113677978516</v>
+        <v>130.5113983154297</v>
       </c>
       <c r="C166" t="n">
         <v>136.6600036621094</v>
@@ -4793,7 +4805,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4820,11 +4832,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>138.5205993652344</v>
+        <v>138.5205535888672</v>
       </c>
       <c r="C168" t="n">
         <v>144.6399993896484</v>
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4874,7 +4886,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4901,11 +4913,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>134.3156433105469</v>
+        <v>134.3156280517578</v>
       </c>
       <c r="C171" t="n">
         <v>139.8600006103516</v>
@@ -4928,11 +4940,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>129.8979797363281</v>
+        <v>129.8979644775391</v>
       </c>
       <c r="C172" t="n">
         <v>135.2599945068359</v>
@@ -4955,11 +4967,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>135.6505126953125</v>
+        <v>135.6505279541016</v>
       </c>
       <c r="C173" t="n">
         <v>141.25</v>
@@ -4982,7 +4994,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5011,11 +5023,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>147.7241973876953</v>
+        <v>147.7242126464844</v>
       </c>
       <c r="C175" t="n">
         <v>153.4199981689453</v>
@@ -5040,11 +5052,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>144.5852355957031</v>
+        <v>144.5852203369141</v>
       </c>
       <c r="C176" t="n">
         <v>150.1600036621094</v>
@@ -5069,11 +5081,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>148.1478271484375</v>
+        <v>148.1478881835938</v>
       </c>
       <c r="C177" t="n">
         <v>153.4400024414062</v>
@@ -5098,11 +5110,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>143.7933654785156</v>
+        <v>143.7933807373047</v>
       </c>
       <c r="C178" t="n">
         <v>148.9299926757812</v>
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>142.403076171875</v>
+        <v>142.4031066894531</v>
       </c>
       <c r="C179" t="n">
         <v>147.4900054931641</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>174.1111297607422</v>
+        <v>174.1111602783203</v>
       </c>
       <c r="C180" t="n">
         <v>179.9100036621094</v>
@@ -5185,11 +5197,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>168.314208984375</v>
+        <v>168.3142242431641</v>
       </c>
       <c r="C181" t="n">
         <v>173.9199981689453</v>
@@ -5214,11 +5226,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>168.8465118408203</v>
+        <v>168.8465270996094</v>
       </c>
       <c r="C182" t="n">
         <v>174.4700012207031</v>
@@ -5243,7 +5255,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5270,11 +5282,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>189.2223205566406</v>
+        <v>189.2222747802734</v>
       </c>
       <c r="C184" t="n">
         <v>195.0399932861328</v>
@@ -5297,11 +5309,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>181.9654235839844</v>
+        <v>181.9654541015625</v>
       </c>
       <c r="C185" t="n">
         <v>187.5599975585938</v>
@@ -5324,11 +5336,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>187.0556488037109</v>
+        <v>187.0556793212891</v>
       </c>
       <c r="C186" t="n">
         <v>192.3899993896484</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>185.9375915527344</v>
+        <v>185.9375457763672</v>
       </c>
       <c r="C187" t="n">
         <v>191.2400054931641</v>
@@ -5378,7 +5390,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5405,11 +5417,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>198.9447021484375</v>
+        <v>198.9446868896484</v>
       </c>
       <c r="C189" t="n">
         <v>204.1399993896484</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>194.3058166503906</v>
+        <v>194.3058471679688</v>
       </c>
       <c r="C190" t="n">
         <v>199.3800048828125</v>
@@ -5459,11 +5471,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>202.5894775390625</v>
+        <v>202.5894927978516</v>
       </c>
       <c r="C191" t="n">
         <v>207.8800048828125</v>
@@ -5486,7 +5498,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5513,7 +5525,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5540,7 +5552,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5567,7 +5579,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5596,11 +5608,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>299.4794921875</v>
+        <v>299.4795837402344</v>
       </c>
       <c r="C196" t="n">
         <v>306.1300048828125</v>
@@ -5625,11 +5637,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>302.8839416503906</v>
+        <v>302.8839111328125</v>
       </c>
       <c r="C197" t="n">
         <v>309.6099853515625</v>
@@ -5654,7 +5666,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5683,7 +5695,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5712,7 +5724,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5741,11 +5753,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>360.0658264160156</v>
+        <v>360.0657653808594</v>
       </c>
       <c r="C201" t="n">
         <v>367</v>
@@ -5770,11 +5782,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>333.4483947753906</v>
+        <v>333.4484252929688</v>
       </c>
       <c r="C202" t="n">
         <v>339.8699951171875</v>
@@ -5799,11 +5811,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>382.0131225585938</v>
+        <v>382.0131530761719</v>
       </c>
       <c r="C203" t="n">
         <v>389.3699951171875</v>
@@ -5828,11 +5840,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>374.9988403320312</v>
+        <v>374.9988708496094</v>
       </c>
       <c r="C204" t="n">
         <v>381.6799926757812</v>
@@ -5857,11 +5869,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>368.5536804199219</v>
+        <v>368.5536499023438</v>
       </c>
       <c r="C205" t="n">
         <v>375.1199951171875</v>
@@ -5886,11 +5898,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>372.0513610839844</v>
+        <v>372.0513916015625</v>
       </c>
       <c r="C206" t="n">
         <v>378.6799926757812</v>
@@ -5915,7 +5927,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5944,11 +5956,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>350.3499145507812</v>
+        <v>350.349853515625</v>
       </c>
       <c r="C208" t="n">
         <v>356.0499877929688</v>
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>358.4088134765625</v>
+        <v>358.4087219238281</v>
       </c>
       <c r="C209" t="n">
         <v>364.239990234375</v>
@@ -6002,11 +6014,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>385.1240844726562</v>
+        <v>385.1241149902344</v>
       </c>
       <c r="C210" t="n">
         <v>390.8399963378906</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>421.0607604980469</v>
+        <v>421.060791015625</v>
       </c>
       <c r="C211" t="n">
         <v>427.3099975585938</v>
@@ -6060,11 +6072,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>396.5150451660156</v>
+        <v>396.5150146484375</v>
       </c>
       <c r="C212" t="n">
         <v>402.3999938964844</v>
@@ -6089,11 +6101,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>406.8883361816406</v>
+        <v>406.8883666992188</v>
       </c>
       <c r="C213" t="n">
         <v>412.3200073242188</v>
@@ -6118,11 +6130,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>429.1214904785156</v>
+        <v>429.1215515136719</v>
       </c>
       <c r="C214" t="n">
         <v>434.8500061035156</v>
@@ -6147,11 +6159,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>449.3612976074219</v>
+        <v>449.361328125</v>
       </c>
       <c r="C215" t="n">
         <v>455.3599853515625</v>
@@ -6176,11 +6188,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>464.9924011230469</v>
+        <v>464.9923706054688</v>
       </c>
       <c r="C216" t="n">
         <v>470.5599975585938</v>
@@ -6205,11 +6217,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>457.5020141601562</v>
+        <v>457.5020751953125</v>
       </c>
       <c r="C217" t="n">
         <v>462.9800109863281</v>
@@ -6234,11 +6246,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>493.9753112792969</v>
+        <v>493.9754028320312</v>
       </c>
       <c r="C218" t="n">
         <v>499.8900146484375</v>
@@ -6263,11 +6275,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>515.8514404296875</v>
+        <v>515.851318359375</v>
       </c>
       <c r="C219" t="n">
         <v>521.4099731445312</v>
@@ -6292,11 +6304,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>531.1267700195312</v>
+        <v>531.1268310546875</v>
       </c>
       <c r="C220" t="n">
         <v>536.8499755859375</v>
@@ -6321,7 +6333,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6350,11 +6362,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>563.5177612304688</v>
+        <v>563.517822265625</v>
       </c>
       <c r="C222" t="n">
         <v>569.5900268554688</v>
@@ -6379,7 +6391,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6408,7 +6420,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6437,11 +6449,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>556.4137573242188</v>
+        <v>556.413818359375</v>
       </c>
       <c r="C225" t="n">
         <v>561.0800170898438</v>
@@ -6466,7 +6478,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6495,11 +6507,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>496.4268493652344</v>
+        <v>496.4268798828125</v>
       </c>
       <c r="C227" t="n">
         <v>500.5899963378906</v>
@@ -6524,7 +6536,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6553,7 +6565,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6582,7 +6594,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6611,7 +6623,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6640,11 +6652,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>668.8895263671875</v>
+        <v>668.8896484375</v>
       </c>
       <c r="C232" t="n">
         <v>672.989990234375</v>
@@ -6669,11 +6681,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>708.4471435546875</v>
+        <v>708.4470825195312</v>
       </c>
       <c r="C233" t="n">
         <v>712.7899780273438</v>
@@ -6698,7 +6710,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6727,7 +6739,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6756,11 +6768,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>689.9952392578125</v>
+        <v>689.9953002929688</v>
       </c>
       <c r="C236" t="n">
         <v>693.5399780273438</v>
@@ -6785,7 +6797,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6814,7 +6826,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6843,11 +6855,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>808.1583251953125</v>
+        <v>808.1582641601562</v>
       </c>
       <c r="C239" t="n">
         <v>811.3400268554688</v>
@@ -6872,11 +6884,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>877.6646118164062</v>
+        <v>877.6646728515625</v>
       </c>
       <c r="C240" t="n">
         <v>881.1199951171875</v>
@@ -6901,7 +6913,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6930,11 +6942,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>828.7216796875</v>
+        <v>828.7216186523438</v>
       </c>
       <c r="C242" t="n">
         <v>831.2100219726562</v>
@@ -6959,11 +6971,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>984.4140625</v>
+        <v>984.4141235351562</v>
       </c>
       <c r="C243" t="n">
         <v>987.3699951171875</v>
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7017,7 +7029,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7075,7 +7087,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7104,7 +7116,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7162,32 +7174,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>880.5</v>
+        <v>869.3599853515625</v>
       </c>
       <c r="C250" t="n">
-        <v>880.5</v>
+        <v>869.3599853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>15307600</v>
+        <v>15901100</v>
       </c>
       <c r="E250" t="n">
         <v>37.28</v>
       </c>
       <c r="F250" t="n">
-        <v>23.61856223175966</v>
+        <v>23.3197420963402</v>
       </c>
       <c r="G250" t="n">
         <v>116590363</v>
       </c>
       <c r="H250" t="n">
-        <v>102657814621.5</v>
+        <v>101358996269.8134</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1312938703175665</v>
+        <v>0.1363843425035052</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7440,7 +7452,7 @@
       <c r="I5" t="n">
         <v>2.95</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="K5" t="n">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7486,7 +7498,7 @@
       <c r="I6" t="n">
         <v>3.18</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="K6" t="n">
@@ -7499,13 +7511,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7532,7 +7544,7 @@
       <c r="I7" t="n">
         <v>3.12</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="K7" t="n">
@@ -7545,13 +7557,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7578,7 +7590,7 @@
       <c r="I8" t="n">
         <v>4.38</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="K8" t="n">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7624,7 +7636,7 @@
       <c r="I9" t="n">
         <v>4.62</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="K9" t="n">
@@ -7637,13 +7649,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7670,7 +7682,7 @@
       <c r="I10" t="n">
         <v>4.66</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="K10" t="n">
@@ -7683,13 +7695,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7716,7 +7728,7 @@
       <c r="I11" t="n">
         <v>4.8</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="K11" t="n">
@@ -7729,13 +7741,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="I12" t="n">
         <v>4.210000000000001</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K12" t="n">
@@ -7775,13 +7787,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7808,7 +7820,7 @@
       <c r="I13" t="n">
         <v>4.57</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K13" t="n">
@@ -7821,13 +7833,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7854,7 +7866,7 @@
       <c r="I14" t="n">
         <v>4.6</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K14" t="n">
@@ -7867,13 +7879,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7900,7 +7912,7 @@
       <c r="I15" t="n">
         <v>4.53</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="K15" t="n">
@@ -7913,13 +7925,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40938</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="I16" t="n">
         <v>5.13</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40938</v>
       </c>
       <c r="K16" t="n">
@@ -7959,13 +7971,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7992,7 +8004,7 @@
       <c r="I17" t="n">
         <v>5.6</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="K17" t="n">
@@ -8005,13 +8017,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8038,7 +8050,7 @@
       <c r="I18" t="n">
         <v>6.05</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K18" t="n">
@@ -8051,13 +8063,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8084,7 +8096,7 @@
       <c r="I19" t="n">
         <v>6.54</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K19" t="n">
@@ -8097,13 +8109,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8130,7 +8142,7 @@
       <c r="I20" t="n">
         <v>6.58</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="K20" t="n">
@@ -8143,13 +8155,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8176,7 +8188,7 @@
       <c r="I21" t="n">
         <v>5.59</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K21" t="n">
@@ -8189,13 +8201,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="I22" t="n">
         <v>5.84</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K22" t="n">
@@ -8235,13 +8247,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8268,7 +8280,7 @@
       <c r="I23" t="n">
         <v>5.91</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K23" t="n">
@@ -8281,13 +8293,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41669</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8314,7 +8326,7 @@
       <c r="I24" t="n">
         <v>4.95</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41669</v>
       </c>
       <c r="K24" t="n">
@@ -8327,13 +8339,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41773</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8360,7 +8372,7 @@
       <c r="I25" t="n">
         <v>5.430000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41773</v>
       </c>
       <c r="K25" t="n">
@@ -8373,13 +8385,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8406,7 +8418,7 @@
       <c r="I26" t="n">
         <v>5.32</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K26" t="n">
@@ -8419,13 +8431,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8452,7 +8464,7 @@
       <c r="I27" t="n">
         <v>5.57</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="K27" t="n">
@@ -8465,13 +8477,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8498,7 +8510,7 @@
       <c r="I28" t="n">
         <v>7.29</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="K28" t="n">
@@ -8511,13 +8523,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42136</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8544,7 +8556,7 @@
       <c r="I29" t="n">
         <v>6.27</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42136</v>
       </c>
       <c r="K29" t="n">
@@ -8557,13 +8569,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8590,7 +8602,7 @@
       <c r="I30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K30" t="n">
@@ -8603,13 +8615,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8636,7 +8648,7 @@
       <c r="I31" t="n">
         <v>7.64</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K31" t="n">
@@ -8649,13 +8661,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8682,7 +8694,7 @@
       <c r="I32" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="K32" t="n">
@@ -8695,13 +8707,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8728,7 +8740,7 @@
       <c r="I33" t="n">
         <v>9.69</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K33" t="n">
@@ -8741,13 +8753,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8774,7 +8786,7 @@
       <c r="I34" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K34" t="n">
@@ -8787,13 +8799,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8820,7 +8832,7 @@
       <c r="I35" t="n">
         <v>8.33</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K35" t="n">
@@ -8833,13 +8845,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8866,7 +8878,7 @@
       <c r="I36" t="n">
         <v>8.449999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="K36" t="n">
@@ -8879,13 +8891,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8912,7 +8924,7 @@
       <c r="I37" t="n">
         <v>23.33</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="K37" t="n">
@@ -8925,13 +8937,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8958,7 +8970,7 @@
       <c r="I38" t="n">
         <v>22.4</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K38" t="n">
@@ -8971,13 +8983,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9004,7 +9016,7 @@
       <c r="I39" t="n">
         <v>21.07</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K39" t="n">
@@ -9017,13 +9029,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9050,7 +9062,7 @@
       <c r="I40" t="n">
         <v>22.55</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="K40" t="n">
@@ -9063,13 +9075,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9096,7 +9108,7 @@
       <c r="I41" t="n">
         <v>0.21</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="K41" t="n">
@@ -9109,13 +9121,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="I42" t="n">
         <v>-1.92</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K42" t="n">
@@ -9155,13 +9167,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9188,7 +9200,7 @@
       <c r="I43" t="n">
         <v>0.5799999999999998</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K43" t="n">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I44" t="n">
         <v>-1.35</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K44" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43600</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I45" t="n">
         <v>0.0600000000000005</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43600</v>
       </c>
       <c r="K45" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I46" t="n">
         <v>2.980000000000001</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K46" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I47" t="n">
         <v>-3.519999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K47" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I48" t="n">
         <v>-4.889999999999999</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="K48" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I49" t="n">
         <v>5.130000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="K49" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I50" t="n">
         <v>5.610000000000001</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="K50" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I51" t="n">
         <v>13.14</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K51" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I52" t="n">
         <v>-26.92</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="K52" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I53" t="n">
         <v>-28.62</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="K53" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I54" t="n">
         <v>-28.27</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K54" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I55" t="n">
         <v>-30.1</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K55" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I56" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K56" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I57" t="n">
         <v>7.23</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="K57" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I58" t="n">
         <v>9.42</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K58" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I59" t="n">
         <v>14.13</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K59" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I60" t="n">
         <v>21.83</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="K60" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I61" t="n">
         <v>25.03</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="K61" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I62" t="n">
         <v>26.79</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K62" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I63" t="n">
         <v>25.29</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K63" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I64" t="n">
         <v>22.05</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K64" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I65" t="n">
         <v>22.39</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K65" t="n">
@@ -10213,13 +10225,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10246,7 +10258,7 @@
       <c r="I66" t="n">
         <v>22.37</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K66" t="n">
@@ -10259,13 +10271,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10292,7 +10304,7 @@
       <c r="I67" t="n">
         <v>19.32</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="K67" t="n">
@@ -10305,13 +10317,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10338,7 +10350,7 @@
       <c r="I68" t="n">
         <v>21.85</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="K68" t="n">
@@ -10351,13 +10363,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10384,7 +10396,7 @@
       <c r="I69" t="n">
         <v>25.72</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="K69" t="n">
@@ -10397,13 +10409,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10430,7 +10442,7 @@
       <c r="I70" t="n">
         <v>24.97</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K70" t="n">
@@ -10443,13 +10455,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10476,7 +10488,7 @@
       <c r="I71" t="n">
         <v>32.02</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K71" t="n">
@@ -10489,13 +10501,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="I72" t="n">
         <v>34.66</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="K72" t="n">
@@ -10535,13 +10547,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10568,7 +10580,7 @@
       <c r="I73" t="n">
         <v>38.38</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="K73" t="n">
@@ -10581,13 +10593,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10614,7 +10626,7 @@
       <c r="I74" t="n">
         <v>37.28</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K74" t="n">
@@ -10651,52 +10663,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="C2" t="n">
@@ -10725,10 +10737,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40113</v>
       </c>
       <c r="C3" t="n">
@@ -10757,10 +10769,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40204</v>
       </c>
       <c r="C4" t="n">
@@ -10789,10 +10801,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10821,10 +10833,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="C6" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40477</v>
       </c>
       <c r="C7" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="C8" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40841</v>
       </c>
       <c r="C11" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40938</v>
       </c>
       <c r="C12" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41031</v>
       </c>
       <c r="C13" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C14" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C15" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="C16" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C18" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C19" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41669</v>
       </c>
       <c r="C20" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41773</v>
       </c>
       <c r="C21" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C22" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41940</v>
       </c>
       <c r="C23" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42040</v>
       </c>
       <c r="C24" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42136</v>
       </c>
       <c r="C25" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C27" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42396</v>
       </c>
       <c r="C28" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C30" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C31" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42761</v>
       </c>
       <c r="C32" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42877</v>
       </c>
       <c r="C33" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C34" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="C36" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43244</v>
       </c>
       <c r="C37" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C38" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C40" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43600</v>
       </c>
       <c r="C41" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C42" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43865</v>
       </c>
       <c r="C44" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="C45" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44046</v>
       </c>
       <c r="C46" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C47" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44229</v>
       </c>
       <c r="C48" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44328</v>
       </c>
       <c r="C49" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C51" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C52" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44690</v>
       </c>
       <c r="C53" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44959</v>
       </c>
       <c r="C56" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45055</v>
       </c>
       <c r="C57" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C60" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C61" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C62" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45603</v>
       </c>
       <c r="C63" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C64" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="C65" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C66" t="n">
@@ -12773,10 +12785,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C67" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="C68" t="n">
@@ -12837,10 +12849,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="C69" t="n">
@@ -12869,10 +12881,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12919,12 +12931,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MCK.xlsx
+++ b/salidas/empresas/MCK.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>45.41146087646484</v>
+        <v>45.41145324707031</v>
       </c>
       <c r="C2" t="n">
         <v>53</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>46.43162155151367</v>
+        <v>46.43164443969727</v>
       </c>
       <c r="C3" t="n">
         <v>54.13000106811523</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>44.716064453125</v>
+        <v>44.71607208251953</v>
       </c>
       <c r="C4" t="n">
         <v>52.13000106811523</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>41.67954254150391</v>
+        <v>41.67952728271484</v>
       </c>
       <c r="C5" t="n">
         <v>48.59000015258789</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>42.4600944519043</v>
+        <v>42.46010971069336</v>
       </c>
       <c r="C6" t="n">
         <v>49.5</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>40.60650634765625</v>
+        <v>40.60649490356445</v>
       </c>
       <c r="C7" t="n">
         <v>47.27999877929688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>43.68072509765625</v>
+        <v>43.68072891235352</v>
       </c>
       <c r="C9" t="n">
         <v>50.79999923706055</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>45.33164978027344</v>
+        <v>45.33166122436523</v>
       </c>
       <c r="C10" t="n">
         <v>52.72000122070312</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>43.07024002075195</v>
+        <v>43.07023239135742</v>
       </c>
       <c r="C11" t="n">
         <v>50.09000015258789</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>42.52954483032227</v>
+        <v>42.52956008911133</v>
       </c>
       <c r="C12" t="n">
         <v>49.40000152587891</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>43.64873886108398</v>
+        <v>43.64875411987305</v>
       </c>
       <c r="C13" t="n">
         <v>50.70000076293945</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>47.99639511108398</v>
+        <v>47.99639892578125</v>
       </c>
       <c r="C14" t="n">
         <v>55.75</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>48.02099609375</v>
+        <v>48.0210075378418</v>
       </c>
       <c r="C15" t="n">
         <v>55.72000122070312</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>50.45134353637695</v>
+        <v>50.45135879516602</v>
       </c>
       <c r="C16" t="n">
         <v>58.54000091552734</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>54.40715789794922</v>
+        <v>54.40714263916016</v>
       </c>
       <c r="C18" t="n">
         <v>63.13000106811523</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>51.44898223876953</v>
+        <v>51.44897842407227</v>
       </c>
       <c r="C19" t="n">
         <v>59.63999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.82718276977539</v>
+        <v>49.82718658447266</v>
       </c>
       <c r="C20" t="n">
         <v>57.7599983215332</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>49.40353012084961</v>
+        <v>49.40351867675781</v>
       </c>
       <c r="C21" t="n">
         <v>57.20999908447266</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>57.08042526245117</v>
+        <v>57.08043670654297</v>
       </c>
       <c r="C23" t="n">
         <v>66.09999847412109</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.67607498168945</v>
+        <v>57.67609405517578</v>
       </c>
       <c r="C24" t="n">
         <v>66.73000335693359</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>56.62164306640625</v>
+        <v>56.62161254882812</v>
       </c>
       <c r="C25" t="n">
         <v>65.51000213623047</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>54.31386566162109</v>
+        <v>54.31389236450195</v>
       </c>
       <c r="C26" t="n">
         <v>62.84000015258789</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>50.83767318725586</v>
+        <v>50.83767700195312</v>
       </c>
       <c r="C27" t="n">
         <v>58.7599983215332</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>45.30920028686523</v>
+        <v>45.3092041015625</v>
       </c>
       <c r="C28" t="n">
         <v>52.36999893188477</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>45.09291839599609</v>
+        <v>45.09289169311523</v>
       </c>
       <c r="C29" t="n">
         <v>52.11999893188477</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>49.87733840942383</v>
+        <v>49.87732696533203</v>
       </c>
       <c r="C30" t="n">
         <v>57.65000152587891</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.4730339050293</v>
+        <v>48.47303009033203</v>
       </c>
       <c r="C31" t="n">
         <v>55.90999984741211</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>48.54239273071289</v>
+        <v>48.54238510131836</v>
       </c>
       <c r="C32" t="n">
         <v>55.9900016784668</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>50.19811630249023</v>
+        <v>50.1981086730957</v>
       </c>
       <c r="C33" t="n">
         <v>57.77999877929688</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>46.74905776977539</v>
+        <v>46.74906921386719</v>
       </c>
       <c r="C34" t="n">
         <v>53.81000137329102</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>31.96243667602539</v>
+        <v>31.96242332458496</v>
       </c>
       <c r="C35" t="n">
         <v>36.79000091552734</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>33.7707405090332</v>
+        <v>33.77074432373047</v>
       </c>
       <c r="C37" t="n">
         <v>38.72999954223633</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>38.54032135009766</v>
+        <v>38.54030609130859</v>
       </c>
       <c r="C38" t="n">
         <v>44.20000076293945</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>35.86600875854492</v>
+        <v>35.86598587036133</v>
       </c>
       <c r="C39" t="n">
         <v>41.02000045776367</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>30.63735580444336</v>
+        <v>30.63737487792969</v>
       </c>
       <c r="C40" t="n">
         <v>35.04000091552734</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>32.35108947753906</v>
+        <v>32.35110473632812</v>
       </c>
       <c r="C41" t="n">
         <v>37</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>35.97964477539062</v>
+        <v>35.97966003417969</v>
       </c>
       <c r="C42" t="n">
         <v>41.15000152587891</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>44.85251235961914</v>
+        <v>44.85252380371094</v>
       </c>
       <c r="C44" t="n">
         <v>51.15000152587891</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>49.9647216796875</v>
+        <v>49.9647102355957</v>
       </c>
       <c r="C45" t="n">
         <v>56.86000061035156</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>52.32852554321289</v>
+        <v>52.3285026550293</v>
       </c>
       <c r="C46" t="n">
         <v>59.54999923706055</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>51.60794067382812</v>
+        <v>51.60795211791992</v>
       </c>
       <c r="C47" t="n">
         <v>58.72999954223633</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>54.60205459594727</v>
+        <v>54.60203552246094</v>
       </c>
       <c r="C48" t="n">
         <v>62.02000045776367</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>55.02463531494141</v>
+        <v>55.0246467590332</v>
       </c>
       <c r="C49" t="n">
         <v>62.5</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>51.78478622436523</v>
+        <v>51.78478240966797</v>
       </c>
       <c r="C50" t="n">
         <v>58.81999969482422</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>52.18096923828125</v>
+        <v>52.18096542358398</v>
       </c>
       <c r="C51" t="n">
         <v>59.15000152587891</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>57.97689056396484</v>
+        <v>57.97686386108398</v>
       </c>
       <c r="C52" t="n">
         <v>65.72000122070312</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>57.17411804199219</v>
+        <v>57.17411422729492</v>
       </c>
       <c r="C53" t="n">
         <v>64.80999755859375</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>61.75263214111328</v>
+        <v>61.75262069702148</v>
       </c>
       <c r="C54" t="n">
         <v>70</v>
@@ -1575,7 +1575,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>59.40231323242188</v>
+        <v>59.40232467651367</v>
       </c>
       <c r="C55" t="n">
         <v>67.16000366210938</v>
@@ -1604,7 +1604,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>55.56362915039062</v>
+        <v>55.56362533569336</v>
       </c>
       <c r="C56" t="n">
         <v>62.81999969482422</v>
@@ -1633,7 +1633,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>51.49818420410156</v>
+        <v>51.49818801879883</v>
       </c>
       <c r="C57" t="n">
         <v>58.04999923706055</v>
@@ -1662,7 +1662,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>54.80719375610352</v>
+        <v>54.80718994140625</v>
       </c>
       <c r="C58" t="n">
         <v>61.77999877929688</v>
@@ -1691,7 +1691,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>58.53316879272461</v>
+        <v>58.53316497802734</v>
       </c>
       <c r="C59" t="n">
         <v>65.98000335693359</v>
@@ -1749,7 +1749,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>62.61124420166016</v>
+        <v>62.61128616333008</v>
       </c>
       <c r="C61" t="n">
         <v>70.37999725341797</v>
@@ -1778,7 +1778,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>66.87253570556641</v>
+        <v>66.87255096435547</v>
       </c>
       <c r="C62" t="n">
         <v>75.16999816894531</v>
@@ -1807,7 +1807,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>70.69154357910156</v>
+        <v>70.69153594970703</v>
       </c>
       <c r="C63" t="n">
         <v>79.27999877929688</v>
@@ -1836,7 +1836,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>70.48646545410156</v>
+        <v>70.48644256591797</v>
       </c>
       <c r="C64" t="n">
         <v>79.05000305175781</v>
@@ -1865,7 +1865,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>74.01748657226562</v>
+        <v>74.01747131347656</v>
       </c>
       <c r="C65" t="n">
         <v>83.01000213623047</v>
@@ -1894,7 +1894,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>76.33580017089844</v>
+        <v>76.3358154296875</v>
       </c>
       <c r="C66" t="n">
         <v>85.61000061035156</v>
@@ -1923,7 +1923,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>74.76541900634766</v>
+        <v>74.76542663574219</v>
       </c>
       <c r="C67" t="n">
         <v>83.65000152587891</v>
@@ -2010,7 +2010,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>65.14521026611328</v>
+        <v>65.14517211914062</v>
       </c>
       <c r="C70" t="n">
         <v>72.69999694824219</v>
@@ -2039,7 +2039,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>73.07554626464844</v>
+        <v>73.07551574707031</v>
       </c>
       <c r="C71" t="n">
         <v>81.55000305175781</v>
@@ -2068,7 +2068,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>73.04716491699219</v>
+        <v>73.04720306396484</v>
       </c>
       <c r="C72" t="n">
         <v>81.30999755859375</v>
@@ -2097,7 +2097,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>69.99267578125</v>
+        <v>69.99270629882812</v>
       </c>
       <c r="C73" t="n">
         <v>77.91000366210938</v>
@@ -2126,7 +2126,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>73.41551971435547</v>
+        <v>73.41552734375</v>
       </c>
       <c r="C74" t="n">
         <v>81.72000122070312</v>
@@ -2155,7 +2155,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>75.20679473876953</v>
+        <v>75.20682525634766</v>
       </c>
       <c r="C75" t="n">
         <v>83.51000213623047</v>
@@ -2184,7 +2184,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>79.04324340820312</v>
+        <v>79.04322814941406</v>
       </c>
       <c r="C76" t="n">
         <v>87.76999664306641</v>
@@ -2213,7 +2213,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>82.32134246826172</v>
+        <v>82.32132720947266</v>
       </c>
       <c r="C77" t="n">
         <v>91.41000366210938</v>
@@ -2271,7 +2271,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>84.62193298339844</v>
+        <v>84.62190246582031</v>
       </c>
       <c r="C79" t="n">
         <v>93.75</v>
@@ -2300,7 +2300,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>81.89597320556641</v>
+        <v>81.89595031738281</v>
       </c>
       <c r="C80" t="n">
         <v>90.73000335693359</v>
@@ -2329,7 +2329,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>78.80772399902344</v>
+        <v>78.80771636962891</v>
       </c>
       <c r="C81" t="n">
         <v>87.11000061035156</v>
@@ -2358,7 +2358,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>77.83067321777344</v>
+        <v>77.83068084716797</v>
       </c>
       <c r="C82" t="n">
         <v>86.02999877929688</v>
@@ -2387,7 +2387,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>84.41683197021484</v>
+        <v>84.41680145263672</v>
       </c>
       <c r="C83" t="n">
         <v>93.30999755859375</v>
@@ -2416,7 +2416,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>85.65053558349609</v>
+        <v>85.65056610107422</v>
       </c>
       <c r="C84" t="n">
         <v>94.47000122070312</v>
@@ -2445,7 +2445,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>87.90805053710938</v>
+        <v>87.90806579589844</v>
       </c>
       <c r="C85" t="n">
         <v>96.95999908447266</v>
@@ -2474,7 +2474,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>95.406005859375</v>
+        <v>95.40596771240234</v>
       </c>
       <c r="C86" t="n">
         <v>105.2300033569336</v>
@@ -2503,7 +2503,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>96.40723419189453</v>
+        <v>96.40724945068359</v>
       </c>
       <c r="C87" t="n">
         <v>106.129997253418</v>
@@ -2561,7 +2561,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>96.1256103515625</v>
+        <v>96.12563323974609</v>
       </c>
       <c r="C89" t="n">
         <v>105.8199996948242</v>
@@ -2590,7 +2590,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>103.429069519043</v>
+        <v>103.4290771484375</v>
       </c>
       <c r="C90" t="n">
         <v>113.8600006103516</v>
@@ -2619,7 +2619,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>104.1959991455078</v>
+        <v>104.1960144042969</v>
       </c>
       <c r="C91" t="n">
         <v>114.5</v>
@@ -2648,7 +2648,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>111.6216659545898</v>
+        <v>111.6217041015625</v>
       </c>
       <c r="C92" t="n">
         <v>122.6600036621094</v>
@@ -2677,7 +2677,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>110.7033920288086</v>
+        <v>110.7033462524414</v>
       </c>
       <c r="C93" t="n">
         <v>121.4100036621094</v>
@@ -2706,7 +2706,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>116.9857940673828</v>
+        <v>116.9857864379883</v>
       </c>
       <c r="C94" t="n">
         <v>128.3000030517578</v>
@@ -2735,7 +2735,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>142.5530242919922</v>
+        <v>142.5530548095703</v>
       </c>
       <c r="C95" t="n">
         <v>156.3399963378906</v>
@@ -2793,7 +2793,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>147.3820190429688</v>
+        <v>147.3820343017578</v>
       </c>
       <c r="C97" t="n">
         <v>161.3999938964844</v>
@@ -2822,7 +2822,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>159.2620544433594</v>
+        <v>159.2621002197266</v>
       </c>
       <c r="C98" t="n">
         <v>174.4100036621094</v>
@@ -2851,7 +2851,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>161.8950805664062</v>
+        <v>161.8951416015625</v>
       </c>
       <c r="C99" t="n">
         <v>177.0500030517578</v>
@@ -2880,7 +2880,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>161.4562072753906</v>
+        <v>161.4561920166016</v>
       </c>
       <c r="C100" t="n">
         <v>176.5700073242188</v>
@@ -2909,7 +2909,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>154.7079162597656</v>
+        <v>154.7079467773438</v>
       </c>
       <c r="C101" t="n">
         <v>169.1900024414062</v>
@@ -2967,7 +2967,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>170.4866790771484</v>
+        <v>170.4867095947266</v>
       </c>
       <c r="C103" t="n">
         <v>186.2100067138672</v>
@@ -2996,7 +2996,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>175.6595611572266</v>
+        <v>175.6596069335938</v>
       </c>
       <c r="C104" t="n">
         <v>191.8600006103516</v>
@@ -3025,7 +3025,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>178.7854309082031</v>
+        <v>178.785400390625</v>
       </c>
       <c r="C105" t="n">
         <v>195.0299987792969</v>
@@ -3054,7 +3054,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>178.4553375244141</v>
+        <v>178.455322265625</v>
       </c>
       <c r="C106" t="n">
         <v>194.6699981689453</v>
@@ -3083,7 +3083,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>186.4673156738281</v>
+        <v>186.4673767089844</v>
       </c>
       <c r="C107" t="n">
         <v>203.4100036621094</v>
@@ -3112,7 +3112,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>193.4273681640625</v>
+        <v>193.4273834228516</v>
       </c>
       <c r="C108" t="n">
         <v>210.7599945068359</v>
@@ -3141,7 +3141,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>190.5089111328125</v>
+        <v>190.5089263916016</v>
       </c>
       <c r="C109" t="n">
         <v>207.5800018310547</v>
@@ -3170,7 +3170,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>195.1619262695312</v>
+        <v>195.1618957519531</v>
       </c>
       <c r="C110" t="n">
         <v>212.6499938964844</v>
@@ -3199,7 +3199,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>210.1116485595703</v>
+        <v>210.1115875244141</v>
       </c>
       <c r="C111" t="n">
         <v>228.6999969482422</v>
@@ -3228,7 +3228,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>207.8148040771484</v>
+        <v>207.8147735595703</v>
       </c>
       <c r="C112" t="n">
         <v>226.1999969482422</v>
@@ -3257,7 +3257,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>205.2424163818359</v>
+        <v>205.2423858642578</v>
       </c>
       <c r="C113" t="n">
         <v>223.3999938964844</v>
@@ -3315,7 +3315,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>206.7471313476562</v>
+        <v>206.7471618652344</v>
       </c>
       <c r="C115" t="n">
         <v>224.8099975585938</v>
@@ -3344,7 +3344,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>202.8478546142578</v>
+        <v>202.8477783203125</v>
       </c>
       <c r="C116" t="n">
         <v>220.5700073242188</v>
@@ -3402,7 +3402,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>170.4032897949219</v>
+        <v>170.4032287597656</v>
       </c>
       <c r="C118" t="n">
         <v>185.0299987792969</v>
@@ -3431,7 +3431,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>164.6658020019531</v>
+        <v>164.665771484375</v>
       </c>
       <c r="C119" t="n">
         <v>178.8000030517578</v>
@@ -3460,7 +3460,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>174.6397399902344</v>
+        <v>174.6397247314453</v>
       </c>
       <c r="C120" t="n">
         <v>189.3500061035156</v>
@@ -3489,7 +3489,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>181.9075164794922</v>
+        <v>181.9075012207031</v>
       </c>
       <c r="C121" t="n">
         <v>197.2299957275391</v>
@@ -3547,7 +3547,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>143.7892456054688</v>
+        <v>143.7892761230469</v>
       </c>
       <c r="C123" t="n">
         <v>155.6199951171875</v>
@@ -3576,7 +3576,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>145.2953643798828</v>
+        <v>145.2953948974609</v>
       </c>
       <c r="C124" t="n">
         <v>157.25</v>
@@ -3605,7 +3605,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>155.0617980957031</v>
+        <v>155.0618286132812</v>
       </c>
       <c r="C125" t="n">
         <v>167.8200073242188</v>
@@ -3634,7 +3634,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>169.2170715332031</v>
+        <v>169.2171325683594</v>
       </c>
       <c r="C126" t="n">
         <v>183.1399993896484</v>
@@ -3663,7 +3663,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>172.7219390869141</v>
+        <v>172.7219848632812</v>
       </c>
       <c r="C127" t="n">
         <v>186.6499938964844</v>
@@ -3692,7 +3692,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>180.0417327880859</v>
+        <v>180.0417785644531</v>
       </c>
       <c r="C128" t="n">
         <v>194.5599975585938</v>
@@ -3750,7 +3750,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>154.5421905517578</v>
+        <v>154.5421752929688</v>
       </c>
       <c r="C130" t="n">
         <v>166.75</v>
@@ -3779,7 +3779,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>117.8598785400391</v>
+        <v>117.8598861694336</v>
       </c>
       <c r="C131" t="n">
         <v>127.1699981689453</v>
@@ -3808,7 +3808,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>133.5429229736328</v>
+        <v>133.5429534912109</v>
       </c>
       <c r="C132" t="n">
         <v>143.8099975585938</v>
@@ -3837,7 +3837,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>130.4228057861328</v>
+        <v>130.4228820800781</v>
       </c>
       <c r="C133" t="n">
         <v>140.4499969482422</v>
@@ -3866,7 +3866,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>129.2156219482422</v>
+        <v>129.2156524658203</v>
       </c>
       <c r="C134" t="n">
         <v>139.1499938964844</v>
@@ -3895,7 +3895,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>139.6710357666016</v>
+        <v>139.6709594726562</v>
       </c>
       <c r="C135" t="n">
         <v>150.1300048828125</v>
@@ -3924,7 +3924,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>137.9312133789062</v>
+        <v>137.9312591552734</v>
       </c>
       <c r="C136" t="n">
         <v>148.2599945068359</v>
@@ -3953,7 +3953,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>128.6558380126953</v>
+        <v>128.6558227539062</v>
       </c>
       <c r="C137" t="n">
         <v>138.2899932861328</v>
@@ -3982,7 +3982,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>151.7281188964844</v>
+        <v>151.7281341552734</v>
       </c>
       <c r="C138" t="n">
         <v>163.0899963378906</v>
@@ -4011,7 +4011,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>153.3403015136719</v>
+        <v>153.3403472900391</v>
       </c>
       <c r="C139" t="n">
         <v>164.5399932861328</v>
@@ -4040,7 +4040,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>150.8520812988281</v>
+        <v>150.8521270751953</v>
       </c>
       <c r="C140" t="n">
         <v>161.8699951171875</v>
@@ -4069,7 +4069,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>139.4691009521484</v>
+        <v>139.4691619873047</v>
       </c>
       <c r="C141" t="n">
         <v>149.3099975585938</v>
@@ -4098,7 +4098,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>143.4856872558594</v>
+        <v>143.4857025146484</v>
       </c>
       <c r="C142" t="n">
         <v>153.6100006103516</v>
@@ -4127,7 +4127,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>128.7924652099609</v>
+        <v>128.7924957275391</v>
       </c>
       <c r="C143" t="n">
         <v>137.8800048828125</v>
@@ -4185,7 +4185,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>146.0066986083984</v>
+        <v>146.006591796875</v>
       </c>
       <c r="C145" t="n">
         <v>155.9499969482422</v>
@@ -4214,7 +4214,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>158.1122283935547</v>
+        <v>158.1122131347656</v>
       </c>
       <c r="C146" t="n">
         <v>168.8800048828125</v>
@@ -4243,7 +4243,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>140.0248565673828</v>
+        <v>140.0248718261719</v>
       </c>
       <c r="C147" t="n">
         <v>149.2299957275391</v>
@@ -4272,7 +4272,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>132.1806030273438</v>
+        <v>132.1806182861328</v>
       </c>
       <c r="C148" t="n">
         <v>140.8699951171875</v>
@@ -4301,7 +4301,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>146.5743713378906</v>
+        <v>146.5743255615234</v>
       </c>
       <c r="C149" t="n">
         <v>156.2100067138672</v>
@@ -4330,7 +4330,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>133.4988403320312</v>
+        <v>133.4988708496094</v>
       </c>
       <c r="C150" t="n">
         <v>141.9400024414062</v>
@@ -4359,7 +4359,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>125.4667205810547</v>
+        <v>125.4667358398438</v>
       </c>
       <c r="C151" t="n">
         <v>133.3999938964844</v>
@@ -4415,7 +4415,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>121.4576568603516</v>
+        <v>121.4576950073242</v>
       </c>
       <c r="C153" t="n">
         <v>128.75</v>
@@ -4442,7 +4442,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>125.1367721557617</v>
+        <v>125.1367950439453</v>
       </c>
       <c r="C154" t="n">
         <v>132.6499938964844</v>
@@ -4469,7 +4469,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>117.6936798095703</v>
+        <v>117.6936645507812</v>
       </c>
       <c r="C155" t="n">
         <v>124.7600021362305</v>
@@ -4498,7 +4498,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>117.8101654052734</v>
+        <v>117.8101348876953</v>
       </c>
       <c r="C156" t="n">
         <v>124.5</v>
@@ -4556,7 +4556,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>121.3586502075195</v>
+        <v>121.3586349487305</v>
       </c>
       <c r="C158" t="n">
         <v>128.25</v>
@@ -4583,7 +4583,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>120.6966247558594</v>
+        <v>120.696647644043</v>
       </c>
       <c r="C159" t="n">
         <v>127.1600036621094</v>
@@ -4610,7 +4610,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>111.1100158691406</v>
+        <v>111.1100082397461</v>
       </c>
       <c r="C160" t="n">
         <v>117.0599975585938</v>
@@ -4637,7 +4637,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>113.1886749267578</v>
+        <v>113.1886978149414</v>
       </c>
       <c r="C161" t="n">
         <v>119.25</v>
@@ -4693,7 +4693,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>127.9621353149414</v>
+        <v>127.9621200561523</v>
       </c>
       <c r="C163" t="n">
         <v>134.3899993896484</v>
@@ -4751,7 +4751,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>132.0489349365234</v>
+        <v>132.0489807128906</v>
       </c>
       <c r="C165" t="n">
         <v>138.2700042724609</v>
@@ -4780,7 +4780,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>130.5113983154297</v>
+        <v>130.5113677978516</v>
       </c>
       <c r="C166" t="n">
         <v>136.6600036621094</v>
@@ -4809,7 +4809,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>127.0160522460938</v>
+        <v>127.0160293579102</v>
       </c>
       <c r="C167" t="n">
         <v>133</v>
@@ -4863,7 +4863,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>132.4679718017578</v>
+        <v>132.4679260253906</v>
       </c>
       <c r="C169" t="n">
         <v>138.3200073242188</v>
@@ -4890,7 +4890,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>136.5765075683594</v>
+        <v>136.5764617919922</v>
       </c>
       <c r="C170" t="n">
         <v>142.6100006103516</v>
@@ -4917,7 +4917,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>134.3156280517578</v>
+        <v>134.3156127929688</v>
       </c>
       <c r="C171" t="n">
         <v>139.8600006103516</v>
@@ -4944,7 +4944,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>129.8979644775391</v>
+        <v>129.8980407714844</v>
       </c>
       <c r="C172" t="n">
         <v>135.2599945068359</v>
@@ -4971,7 +4971,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>135.6505279541016</v>
+        <v>135.6505432128906</v>
       </c>
       <c r="C173" t="n">
         <v>141.25</v>
@@ -5085,7 +5085,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>148.1478881835938</v>
+        <v>148.1478729248047</v>
       </c>
       <c r="C177" t="n">
         <v>153.4400024414062</v>
@@ -5114,7 +5114,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>143.7933807373047</v>
+        <v>143.7933654785156</v>
       </c>
       <c r="C178" t="n">
         <v>148.9299926757812</v>
@@ -5143,7 +5143,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>142.4031066894531</v>
+        <v>142.4030914306641</v>
       </c>
       <c r="C179" t="n">
         <v>147.4900054931641</v>
@@ -5201,7 +5201,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>168.3142242431641</v>
+        <v>168.314208984375</v>
       </c>
       <c r="C181" t="n">
         <v>173.9199981689453</v>
@@ -5259,7 +5259,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>164.0560150146484</v>
+        <v>164.0560760498047</v>
       </c>
       <c r="C183" t="n">
         <v>169.5200042724609</v>
@@ -5286,7 +5286,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>189.2222747802734</v>
+        <v>189.2223052978516</v>
       </c>
       <c r="C184" t="n">
         <v>195.0399932861328</v>
@@ -5313,7 +5313,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>181.9654541015625</v>
+        <v>181.9654388427734</v>
       </c>
       <c r="C185" t="n">
         <v>187.5599975585938</v>
@@ -5340,7 +5340,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>187.0556793212891</v>
+        <v>187.0556488037109</v>
       </c>
       <c r="C186" t="n">
         <v>192.3899993896484</v>
@@ -5394,7 +5394,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>198.1784820556641</v>
+        <v>198.1785125732422</v>
       </c>
       <c r="C188" t="n">
         <v>203.8300018310547</v>
@@ -5421,7 +5421,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>198.9446868896484</v>
+        <v>198.9446563720703</v>
       </c>
       <c r="C189" t="n">
         <v>204.1399993896484</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>194.3058471679688</v>
+        <v>194.3058319091797</v>
       </c>
       <c r="C190" t="n">
         <v>199.3800048828125</v>
@@ -5475,7 +5475,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>202.5894927978516</v>
+        <v>202.5895080566406</v>
       </c>
       <c r="C191" t="n">
         <v>207.8800048828125</v>
@@ -5502,7 +5502,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>211.6891174316406</v>
+        <v>211.6890869140625</v>
       </c>
       <c r="C192" t="n">
         <v>216.7599945068359</v>
@@ -5556,7 +5556,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>250.7142791748047</v>
+        <v>250.71435546875</v>
       </c>
       <c r="C194" t="n">
         <v>256.7200012207031</v>
@@ -5583,7 +5583,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>268.9867248535156</v>
+        <v>268.9866943359375</v>
       </c>
       <c r="C195" t="n">
         <v>274.9599914550781</v>
@@ -5670,7 +5670,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>322.0012512207031</v>
+        <v>322.0012817382812</v>
       </c>
       <c r="C198" t="n">
         <v>328.6900024414062</v>
@@ -5728,7 +5728,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>334.6289672851562</v>
+        <v>334.6289367675781</v>
       </c>
       <c r="C200" t="n">
         <v>341.5799865722656</v>
@@ -5757,7 +5757,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>360.0657653808594</v>
+        <v>360.0658264160156</v>
       </c>
       <c r="C201" t="n">
         <v>367</v>
@@ -5902,7 +5902,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>372.0513916015625</v>
+        <v>372.0513610839844</v>
       </c>
       <c r="C206" t="n">
         <v>378.6799926757812</v>
@@ -5931,7 +5931,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>344.2097778320312</v>
+        <v>344.2098083496094</v>
       </c>
       <c r="C207" t="n">
         <v>349.8099975585938</v>
@@ -5960,7 +5960,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>350.349853515625</v>
+        <v>350.3499145507812</v>
       </c>
       <c r="C208" t="n">
         <v>356.0499877929688</v>
@@ -5989,7 +5989,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>358.4087219238281</v>
+        <v>358.4087524414062</v>
       </c>
       <c r="C209" t="n">
         <v>364.239990234375</v>
@@ -6076,7 +6076,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>396.5150146484375</v>
+        <v>396.5150451660156</v>
       </c>
       <c r="C212" t="n">
         <v>402.3999938964844</v>
@@ -6105,7 +6105,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>406.8883666992188</v>
+        <v>406.8883361816406</v>
       </c>
       <c r="C213" t="n">
         <v>412.3200073242188</v>
@@ -6134,7 +6134,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>429.1215515136719</v>
+        <v>429.1215209960938</v>
       </c>
       <c r="C214" t="n">
         <v>434.8500061035156</v>
@@ -6192,7 +6192,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>464.9923706054688</v>
+        <v>464.9924011230469</v>
       </c>
       <c r="C216" t="n">
         <v>470.5599975585938</v>
@@ -6221,7 +6221,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>457.5020751953125</v>
+        <v>457.5020446777344</v>
       </c>
       <c r="C217" t="n">
         <v>462.9800109863281</v>
@@ -6279,7 +6279,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>515.851318359375</v>
+        <v>515.8513793945312</v>
       </c>
       <c r="C219" t="n">
         <v>521.4099731445312</v>
@@ -6308,7 +6308,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>531.1268310546875</v>
+        <v>531.1268920898438</v>
       </c>
       <c r="C220" t="n">
         <v>536.8499755859375</v>
@@ -6366,7 +6366,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>563.517822265625</v>
+        <v>563.5177612304688</v>
       </c>
       <c r="C222" t="n">
         <v>569.5900268554688</v>
@@ -6424,7 +6424,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>611.107421875</v>
+        <v>611.1073608398438</v>
       </c>
       <c r="C224" t="n">
         <v>617.02001953125</v>
@@ -6453,7 +6453,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>556.413818359375</v>
+        <v>556.4136352539062</v>
       </c>
       <c r="C225" t="n">
         <v>561.0800170898438</v>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>490.3081359863281</v>
+        <v>490.30810546875</v>
       </c>
       <c r="C226" t="n">
         <v>494.4200134277344</v>
@@ -6511,7 +6511,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>496.4268798828125</v>
+        <v>496.4268188476562</v>
       </c>
       <c r="C227" t="n">
         <v>500.5899963378906</v>
@@ -6569,7 +6569,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>565.8093872070312</v>
+        <v>565.8095092773438</v>
       </c>
       <c r="C229" t="n">
         <v>569.9099731445312</v>
@@ -6598,7 +6598,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>590.4707641601562</v>
+        <v>590.4708251953125</v>
       </c>
       <c r="C230" t="n">
         <v>594.75</v>
@@ -6627,7 +6627,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>635.6533203125</v>
+        <v>635.6533813476562</v>
       </c>
       <c r="C231" t="n">
         <v>640.260009765625</v>
@@ -6772,7 +6772,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>689.9953002929688</v>
+        <v>689.9952392578125</v>
       </c>
       <c r="C236" t="n">
         <v>693.5399780273438</v>
@@ -6801,7 +6801,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>683.1305541992188</v>
+        <v>683.130615234375</v>
       </c>
       <c r="C237" t="n">
         <v>686.6400146484375</v>
@@ -6859,7 +6859,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>808.1582641601562</v>
+        <v>808.1583251953125</v>
       </c>
       <c r="C239" t="n">
         <v>811.3400268554688</v>
@@ -6888,7 +6888,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>877.6646728515625</v>
+        <v>877.6646118164062</v>
       </c>
       <c r="C240" t="n">
         <v>881.1199951171875</v>
@@ -6917,7 +6917,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>817.8342895507812</v>
+        <v>817.834228515625</v>
       </c>
       <c r="C241" t="n">
         <v>820.2899780273438</v>
@@ -6975,7 +6975,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>984.4141235351562</v>
+        <v>984.4140625</v>
       </c>
       <c r="C243" t="n">
         <v>987.3699951171875</v>
